--- a/docs/Anforderungskatalog_16092026.xlsx
+++ b/docs/Anforderungskatalog_16092026.xlsx
@@ -414,7 +414,7 @@
     </x:row>
     <x:row r="2" ht="28" customHeight="1">
       <x:c r="A2" s="12" t="str">
-        <x:v>Fachstand 18.09.2026 – eingefroren; 54 aktive Anforderungen</x:v>
+        <x:v>Fachstand 18.09.2026; A-07 auf Nutzeranweisung am 19.09.2026 geändert; 54 aktive Anforderungen</x:v>
       </x:c>
       <x:c r="B2" s="12"/>
       <x:c r="C2" s="12"/>
@@ -941,13 +941,13 @@
       <x:c r="D52" s="17"/>
       <x:c r="E52" s="17"/>
     </x:row>
-    <x:row r="53" ht="44" customHeight="1">
+    <x:row r="53" ht="92" customHeight="1">
       <x:c r="A53" s="17"/>
       <x:c r="B53" s="17" t="str">
         <x:v>A-07</x:v>
       </x:c>
       <x:c r="C53" s="17" t="str">
-        <x:v>Die grüne Kategorieübersicht muss eine Tabelle mit einer Zeile je eingeschlossenem Mitarbeiter anzeigen: Name des Mitarbeiters und alle von ihm getragenen grünen Soll-Skills.</x:v>
+        <x:v>Die grüne Kategorieübersicht muss eine Tabelle mit einer Zeile je grünem Soll-Skill anzeigen: zuerst die Skill-Bezeichnung, danach alle eingeschlossenen Mitarbeitenden, die diesen Skill tragen. Ein Klick auf die Skill-Bezeichnung öffnet unabhängig von der Mitarbeitermaske den allgemeinen Entwicklungspfad gemäß S-01/S-07; ist kein geschätzter Pfad verfügbar, erscheint die schließbare Warnbox.</x:v>
       </x:c>
       <x:c r="D53" s="17"/>
       <x:c r="E53" s="17"/>

--- a/docs/Anforderungskatalog_16092026.xlsx
+++ b/docs/Anforderungskatalog_16092026.xlsx
@@ -414,7 +414,7 @@
     </x:row>
     <x:row r="2" ht="28" customHeight="1">
       <x:c r="A2" s="12" t="str">
-        <x:v>Fachstand 18.09.2026; A-07 auf Nutzeranweisung am 19.09.2026 geändert; 54 aktive Anforderungen</x:v>
+        <x:v>Fachstand 18.09.2026; A-07 am 19.09.2026 und F-02 (Graphversuch) am 20.09.2026 auf Nutzeranweisung geändert; 54 aktive Anforderungen</x:v>
       </x:c>
       <x:c r="B2" s="12"/>
       <x:c r="C2" s="12"/>
@@ -749,13 +749,13 @@
       <x:c r="D34" s="17"/>
       <x:c r="E34" s="17"/>
     </x:row>
-    <x:row r="35" ht="60" customHeight="1">
+    <x:row r="35" ht="180" customHeight="1">
       <x:c r="A35" s="17"/>
       <x:c r="B35" s="17" t="str">
         <x:v>F-02</x:v>
       </x:c>
       <x:c r="C35" s="17" t="str">
-        <x:v>Die Taxonomie muss als hierarchisches, auf- und zuklappbares Inhaltsverzeichnis umgesetzt werden. Gruppen ohne Untergruppen öffnen ihre Skill-Liste im Mainframe. Die Taxonomie wird im MVA nicht als Graph dargestellt; der separate Entwicklungs-DAG bleibt bestehen.</x:v>
+        <x:v>Die Taxonomie muss zum visuellen Vergleich zwischen hierarchischem, auf- und zuklappbarem Inhaltsverzeichnis und aufklappbarem Gruppengraphen umschaltbar sein. Die Graphansicht ist für diesen Versuch die Startansicht. Ein Klick auf eine Gruppe mit Untergruppen blendet deren direkte Untergruppen ein oder aus; Gruppen ohne Untergruppen öffnen ihre Skill-Liste im Mainframe. Skills erscheinen nicht als Graphknoten. Die Kreise übernehmen die Gruppenbewertung und zeigen die Anzahl aller eindeutigen Skills im aktuellen Maskenausschnitt unterhalb der Gruppe einschließlich direkt zugeordneter Skills, unabhängig vom Aufklappzustand. Gruppennamen stehen unter den Kreisen. Der separate Entwicklungs-DAG bleibt bestehen.</x:v>
       </x:c>
       <x:c r="D35" s="17"/>
       <x:c r="E35" s="17"/>

--- a/docs/Anforderungskatalog_16092026.xlsx
+++ b/docs/Anforderungskatalog_16092026.xlsx
@@ -414,7 +414,7 @@
     </row>
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="12" t="str">
-        <v>Fachstand 18.09.2026 mit freigegebenen Revisionen bis 21.09.2026; 54 aktive Anforderungen, keine neuen IDs</v>
+        <v>Fachstand 18.09.2026 mit freigegebenen Revisionen bis 24.09.2026; 54 aktive Anforderungen, keine neuen IDs</v>
       </c>
       <c r="B2" s="12"/>
       <c r="C2" s="12"/>
@@ -492,13 +492,13 @@
       <c r="D9" s="16"/>
       <c r="E9" s="16"/>
     </row>
-    <row r="10" ht="44" customHeight="1">
+    <row r="10" ht="150" customHeight="1">
       <c r="A10" s="17"/>
       <c r="B10" s="17" t="str">
         <v>G-06</v>
       </c>
       <c r="C10" s="17" t="str">
-        <v>Jeder Mitarbeiter wird genau einer Organisationseinheit zugeordnet; eine gleichzeitige Zuordnung zu mehreren Organisationseinheiten ist ausgeschlossen.</v>
+        <v>Mitarbeitende und Aufgaben werden Organisationseinheiten über m:n-Zuordnungen zugeordnet. Derselbe Mitarbeiter und dieselbe Aufgabe können mehreren Einheiten angehören, ohne ihre Stammdatensätze zu duplizieren. Vorher- und Nachher-Stände werden als getrennte vorbereitete Organisationseinheiten betrachtet. Direkte Mitarbeiter-Skills werden je Organisationszuordnung separat gespeichert; derselbe Skill darf für dieselbe Person in mehreren Einheiten vorkommen, innerhalb einer Einheit jedoch nur einmal. Skillzuordnungen setzen eine gültige Organisationszuordnung der Person voraus.</v>
       </c>
       <c r="D10" s="17"/>
       <c r="E10" s="17"/>
@@ -567,13 +567,13 @@
       <c r="D16" s="16"/>
       <c r="E16" s="16"/>
     </row>
-    <row r="17" ht="150" customHeight="1">
+    <row r="17" ht="105" customHeight="1">
       <c r="A17" s="17"/>
       <c r="B17" s="17" t="str">
         <v>G-05</v>
       </c>
       <c r="C17" s="17" t="str">
-        <v>Das Webinterface sollte eine funktionsfähige Auswahl der in der Datenbank vorhandenen Organisationseinheiten anbieten. Ein Wechsel lädt ausschließlich die Aufgaben und Mitarbeitenden der gewählten Einheit und setzt Simulation, Masken, Navigation, Ansicht und Distanzgrenze auf den Ausgangszustand zurück. Daraus entsteht keine Verwaltungsfunktion.</v>
+        <v>Das Webinterface sollte eine funktionsfähige Auswahl der in der Datenbank vorhandenen Organisationseinheiten anbieten. Ein Wechsel lädt ausschließlich die zugeordneten Aufgaben und Mitarbeitenden sowie die für diese Einheit gespeicherten Mitarbeiter-Skills und setzt Simulation, Masken, Navigation, Ansicht und Distanzgrenze auf den Ausgangszustand zurück. Daraus entsteht keine Verwaltungsfunktion.</v>
       </c>
       <c r="D17" s="17"/>
       <c r="E17" s="17"/>
@@ -627,24 +627,24 @@
       <c r="D22" s="17"/>
       <c r="E22" s="17"/>
     </row>
-    <row r="23" ht="60" customHeight="1">
+    <row r="23" ht="105" customHeight="1">
       <c r="A23" s="17"/>
       <c r="B23" s="17" t="str">
         <v>D-07</v>
       </c>
       <c r="C23" s="17" t="str">
-        <v>Für jede eingeschlossene Aufgabe müssen ihre direkt zugeordneten Skills und sämtliche eindeutigen direkten und indirekten Voraussetzungen als benötigt gelten. Die impliziten Zuordnungen werden bei der Auswertung hergeleitet und nicht zusätzlich dauerhaft gespeichert.</v>
+        <v>Für jede eingeschlossene Aufgabe müssen ihre direkt zugeordneten Skills und sämtliche eindeutigen direkten und indirekten Voraussetzungen als benötigt gelten. Die direkten Skillanforderungen einer Aufgabe gelten in allen zugeordneten Organisationseinheiten identisch. Die impliziten Zuordnungen werden bei der Auswertung hergeleitet und nicht zusätzlich dauerhaft gespeichert.</v>
       </c>
       <c r="D23" s="17"/>
       <c r="E23" s="17"/>
     </row>
-    <row r="24" ht="60" customHeight="1">
+    <row r="24" ht="105" customHeight="1">
       <c r="A24" s="17"/>
       <c r="B24" s="17" t="str">
         <v>D-08</v>
       </c>
       <c r="C24" s="17" t="str">
-        <v>Für jeden Mitarbeiter müssen seine direkt zugeordneten Skills und sämtliche eindeutigen direkten und indirekten Voraussetzungen als vorhanden gelten. Die impliziten Zuordnungen werden bei der Auswertung hergeleitet und nicht zusätzlich dauerhaft gespeichert.</v>
+        <v>Für jeden eingeschlossenen Mitarbeiter müssen ausschließlich seine in der ausgewählten Organisationseinheit direkt zugeordneten Skills und sämtliche eindeutigen direkten und indirekten Voraussetzungen als vorhanden gelten. Skillzuordnungen derselben Person in anderen Einheiten werden nicht übernommen. Die impliziten Zuordnungen werden bei der Auswertung hergeleitet und nicht zusätzlich dauerhaft gespeichert.</v>
       </c>
       <c r="D24" s="17"/>
       <c r="E24" s="17"/>

--- a/docs/Anforderungskatalog_16092026.xlsx
+++ b/docs/Anforderungskatalog_16092026.xlsx
@@ -1007,13 +1007,13 @@
       <c r="D58" s="17"/>
       <c r="E58" s="17"/>
     </row>
-    <row r="59" ht="60" customHeight="1">
+    <row r="59" ht="180" customHeight="1">
       <c r="A59" s="17"/>
       <c r="B59" s="17" t="str">
         <v>A-13</v>
       </c>
       <c r="C59" s="17" t="str">
-        <v>Aufgaben und Mitarbeitende müssen über ein Simulationsmenü temporär aus- und wieder eingeschlossen werden können. Ausgeschlossene Aufgaben tragen nicht zum Soll bei; ausgeschlossene Mitarbeitende nicht zum Ist oder Kandidatenpool. Stammdaten und persistente Zuordnungen bleiben unverändert.</v>
+        <v>Aufgaben und Mitarbeitende müssen über ein Simulationsmenü temporär aus- und wieder eingeschlossen werden können. Ausgeschlossene Aufgaben tragen nicht zum Soll bei; ausgeschlossene Mitarbeitende nicht zum Ist oder Kandidatenpool. Stammdaten und persistente Zuordnungen bleiben unverändert. Bei Aktivierung eines vorbereiteten Szenarios bestimmen dessen Einträge in scenario_task die ausgeschlossenen Aufgaben der gewählten Organisationseinheit; alle nicht zugeordneten Aufgaben bleiben eingeschlossen. Die Szenarioauswahl ersetzt die bisherigen Aufgabenausschlüsse und erhält Mitarbeiterausschlüsse. Ein Szenario ohne Aufgabenzuordnungen schließt keine Aufgabe aus. Bestehende Szenariozuordnungen werden ohne Migration als Ausschlüsse interpretiert. Der Hovertext lautet: Szenario "[Szenarioname]" aktivieren.</v>
       </c>
       <c r="D59" s="17"/>
       <c r="E59" s="17"/>

--- a/docs/Anforderungskatalog_16092026.xlsx
+++ b/docs/Anforderungskatalog_16092026.xlsx
@@ -414,7 +414,7 @@
     </row>
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="12" t="str">
-        <v>Fachstand 18.09.2026 mit freigegebenen Revisionen bis 24.09.2026; 54 aktive Anforderungen, keine neuen IDs</v>
+        <v>Fachstand 18.09.2026 mit freigegebenen Revisionen bis 25.09.2026; 54 aktive Anforderungen, keine neuen IDs</v>
       </c>
       <c r="B2" s="12"/>
       <c r="C2" s="12"/>
@@ -1102,13 +1102,13 @@
       <c r="D67" s="17"/>
       <c r="E67" s="17"/>
     </row>
-    <row r="68" ht="76" customHeight="1">
+    <row r="68" ht="210" customHeight="1">
       <c r="A68" s="17"/>
       <c r="B68" s="17" t="str">
         <v>S-04</v>
       </c>
       <c r="C68" s="17" t="str">
-        <v>Die Auswahl eines Kandidaten aus einer Handlungsempfehlung oder der Aufruf eines Skills mit ausgewählter Person muss den personenbezogenen verbleibenden Entwicklungspfad zum Zielskill öffnen, sofern der Skill gemäß S-01 geschätzt ist. In der Pfadansicht muss der Personenbezug gewechselt oder über Allgemein aufgehoben werden können.</v>
+        <v>Die Auswahl eines Kandidaten aus einer Handlungsempfehlung oder der Aufruf eines Skills mit ausgewählter Person muss den personenbezogenen verbleibenden Entwicklungspfad zum Zielskill öffnen, sofern der Skill gemäß S-01 geschätzt ist. In der Pfadansicht muss der Personenbezug gewechselt oder über Allgemein aufgehoben werden können. Die personenbezogene Pfadansicht bietet dieselbe zielskillbezogene Aufgabenzuordnung wie die allgemeine Ansicht gemäß S-07; Personenauswahl und Pfadumfang verändern diese Liste nicht.</v>
       </c>
       <c r="D68" s="17"/>
       <c r="E68" s="17"/>
@@ -1135,13 +1135,13 @@
       <c r="D70" s="17"/>
       <c r="E70" s="17"/>
     </row>
-    <row r="71" ht="60" customHeight="1">
+    <row r="71" ht="255" customHeight="1">
       <c r="A71" s="17"/>
       <c r="B71" s="17" t="str">
         <v>S-07</v>
       </c>
       <c r="C71" s="17" t="str">
-        <v>Ein Skillaufruf ohne ausgewählte Person muss bei Verfügbarkeit gemäß S-01 den vollständigen allgemeinen DAG ohne personenbezogene Besitzbewertung öffnen. Die Organisationsmaske darf keine Voraussetzungen aus Berechnung oder fachlichem Umfang des gewählten DAGs entfernen.</v>
+        <v>Ein Skillaufruf ohne ausgewählte Person muss bei Verfügbarkeit gemäß S-01 den vollständigen allgemeinen DAG ohne personenbezogene Besitzbewertung öffnen. Die Organisationsmaske darf keine Voraussetzungen aus Berechnung oder fachlichem Umfang des gewählten DAGs entfernen. Der Knopf „Aufgabenzuordnung“ öffnet ein modales Popup mit den Aufgaben, die genau den Zielskill direkt oder als direkte beziehungsweise indirekte Voraussetzung ihrer zugeordneten Skills benötigen, ausschließlich innerhalb der ausgewählten Organisationseinheit. Jede Aufgabe erscheint einmal, auch bei mehreren Vererbungswegen. Temporär ausgeschlossene Aufgaben bleiben mit dem Hinweis „in Simulation ausgeschlossen“ sichtbar. Die Anzeige lautet „Aufgabe [ID] • [Aufgabenname]“; bei leerem Namen steht „kein Aufgabenname hinterlegt“. Ohne Zuordnung erscheint ein Leerhinweis. Der Inhalt ist bei Überlänge scrollbar; Überschrift und Schließen-Knopf bleiben sichtbar. Schließen erhält Ansicht, Auswahl und Scrollposition.</v>
       </c>
       <c r="D71" s="17"/>
       <c r="E71" s="17"/>
